--- a/artfynd/A 55240-2021 artfynd.xlsx
+++ b/artfynd/A 55240-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55240-2021 artfynd.xlsx
+++ b/artfynd/A 55240-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99059446</v>
+        <v>99059438</v>
       </c>
       <c r="B2" t="n">
-        <v>77665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229569</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Varglavsknöl</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phacopsis vulpina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tul.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372805.9660810448</v>
+        <v>372841</v>
       </c>
       <c r="R2" t="n">
-        <v>6919048.111537815</v>
+        <v>6918990</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99059443</v>
+        <v>99059439</v>
       </c>
       <c r="B3" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372808.3343335725</v>
+        <v>372807</v>
       </c>
       <c r="R3" t="n">
-        <v>6919024.802198412</v>
+        <v>6919001</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +847,9 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99059440</v>
+        <v>99059443</v>
       </c>
       <c r="B4" t="n">
-        <v>77665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229569</v>
+        <v>967</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Varglavsknöl</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phacopsis vulpina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tul.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372806.5054781208</v>
+        <v>372808</v>
       </c>
       <c r="R4" t="n">
-        <v>6919001.188049432</v>
+        <v>6919025</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,24 +948,9 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grenar på levande tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99059438</v>
+        <v>99059445</v>
       </c>
       <c r="B5" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372840.928843561</v>
+        <v>372806</v>
       </c>
       <c r="R5" t="n">
-        <v>6918989.197139962</v>
+        <v>6919048</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,19 +1049,9 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99059445</v>
+        <v>99059447</v>
       </c>
       <c r="B6" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372805.9660810448</v>
+        <v>372813</v>
       </c>
       <c r="R6" t="n">
-        <v>6919048.111537815</v>
+        <v>6919049</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1220,19 +1150,9 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99059439</v>
+        <v>99114501</v>
       </c>
       <c r="B7" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,19 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Övre Mysklan, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372806.5054781208</v>
+        <v>372819</v>
       </c>
       <c r="R7" t="n">
-        <v>6919001.188049432</v>
+        <v>6918990</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,28 +1248,17 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1376,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99059444</v>
+        <v>99059437</v>
       </c>
       <c r="B8" t="n">
-        <v>77665</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372808.3343335725</v>
+        <v>372841</v>
       </c>
       <c r="R8" t="n">
-        <v>6919024.802198412</v>
+        <v>6918990</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,19 +1348,14 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,15 +1383,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99059448</v>
+        <v>99059440</v>
       </c>
       <c r="B9" t="n">
-        <v>77665</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372812.984761424</v>
+        <v>372807</v>
       </c>
       <c r="R9" t="n">
-        <v>6919049.237560304</v>
+        <v>6919001</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1568,24 +1454,14 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På grenar av levande tall</t>
+          <t>På grenar på levande tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,15 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99059437</v>
+        <v>99059444</v>
       </c>
       <c r="B10" t="n">
-        <v>77665</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,10 +1527,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372840.928843561</v>
+        <v>372808</v>
       </c>
       <c r="R10" t="n">
-        <v>6918989.197139962</v>
+        <v>6919025</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,24 +1560,9 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,37 +1590,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99059447</v>
+        <v>99059446</v>
       </c>
       <c r="B11" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>967</v>
+        <v>229569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Varglavsknöl</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Phacopsis vulpina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>Tul.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1777,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372812.984761424</v>
+        <v>372806</v>
       </c>
       <c r="R11" t="n">
-        <v>6919049.237560304</v>
+        <v>6919048</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1810,19 +1661,9 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,50 +1691,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99114501</v>
+        <v>99059448</v>
       </c>
       <c r="B12" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>967</v>
+        <v>229569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Varglavsknöl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Phacopsis vulpina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>Tul.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Övre Mysklan, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372818.6380985702</v>
+        <v>372813</v>
       </c>
       <c r="R12" t="n">
-        <v>6918990.045351099</v>
+        <v>6919049</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1923,19 +1762,14 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grenar av levande tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,6 +1778,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55240-2021 artfynd.xlsx
+++ b/artfynd/A 55240-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059438</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059439</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059443</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059445</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059447</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99114501</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059437</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059440</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059446</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,8 +1849,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99059448</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>